--- a/output/pdf_financials_xlsx/SYH.xlsx
+++ b/output/pdf_financials_xlsx/SYH.xlsx
@@ -6007,46 +6007,46 @@
         <v>2.303569</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.650741</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.661969</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.040615</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.291531</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.317084</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.848025</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.914477</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.305029</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.318301</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.843799</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.731402</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.741619</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>8.406446000000001</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.299663000000001</v>
       </c>
     </row>
     <row r="93">
@@ -9825,7 +9825,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10689,7 +10693,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11237,7 +11245,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SYH.xlsx
+++ b/output/pdf_financials_xlsx/SYH.xlsx
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.027541</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00018</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1041,43 +1041,43 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008940999999999999</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00464</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004578</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00315</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.00856</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.022915</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.015012</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.005643</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.004136</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.009469999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.07949000000000001</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.140976</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.140678</v>
       </c>
     </row>
     <row r="13">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.42605</v>
+        <v>-1.453591</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.659366</v>
+        <v>-0.659546</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.404298</v>
@@ -1985,43 +1985,43 @@
         <v>-0.587277</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.571566</v>
+        <v>-1.580507</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.491634</v>
+        <v>-1.496274</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.421756</v>
+        <v>-1.426334</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.584237</v>
+        <v>-0.587387</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.455614</v>
+        <v>-1.464174</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.994947</v>
+        <v>-1.017862</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.666196</v>
+        <v>-1.681208</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.481882</v>
+        <v>-1.487525</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.8720290000000001</v>
+        <v>-0.876165</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.779372</v>
+        <v>-2.788842</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.114013</v>
+        <v>-5.193503</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.813478</v>
+        <v>-4.954454</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.106983</v>
+        <v>-0.247661</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.42605</v>
+        <v>-1.453591</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.659366</v>
+        <v>-0.659546</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.404298</v>
@@ -2101,43 +2101,43 @@
         <v>-0.587277</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.571566</v>
+        <v>-1.580507</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.491634</v>
+        <v>-1.496274</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.421756</v>
+        <v>-1.426334</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.584237</v>
+        <v>-0.587387</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.455614</v>
+        <v>-1.464174</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.994947</v>
+        <v>-1.017862</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.666196</v>
+        <v>-1.681208</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.481882</v>
+        <v>-1.487525</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.8720290000000001</v>
+        <v>-0.876165</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.779372</v>
+        <v>-2.788842</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.114013</v>
+        <v>-5.193503</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.812604</v>
+        <v>-4.95358</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.105498</v>
+        <v>-0.246176</v>
       </c>
     </row>
     <row r="30">
@@ -2402,28 +2402,28 @@
         <v>0.020997</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.012349</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.84573</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.536635</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.369834</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.992366</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.139074</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.201428</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.292313</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>1.352374</v>
@@ -2518,28 +2518,28 @@
         <v>0.038792</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.012349</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.84573</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.536635</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.315338</v>
+        <v>0.685172</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.045979</v>
+        <v>1.038345</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.139074</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.06</v>
+        <v>2.261428</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.28125</v>
+        <v>1.573563</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>1.352374</v>
@@ -3214,28 +3214,28 @@
         <v>0.004683</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.017224</v>
+        <v>0.004875</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.85048</v>
+        <v>0.00475</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.567623</v>
+        <v>0.030988</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.492906</v>
+        <v>0.123072</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.009156</v>
+        <v>0.01679</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.143846</v>
+        <v>0.004772</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.338594</v>
+        <v>0.137166</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.320549</v>
+        <v>0.028236</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.072864</v>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -37065,7 +37065,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E329" s="5" t="n">

--- a/output/pdf_financials_xlsx/SYH.xlsx
+++ b/output/pdf_financials_xlsx/SYH.xlsx
@@ -1319,13 +1319,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.09590799999999999</v>
+        <v>-0.09590799999999999</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.064</v>
+        <v>-0.064</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.001675</v>
+        <v>-0.041791</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2245,7 +2245,7 @@
         <v>-9.706293621448483</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.06966690485122892</v>
+        <v>-1.738178877992661</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01985</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005826</v>
       </c>
       <c r="R111" s="3" t="n">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.02343</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.012082</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7330,40 +7330,40 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.048923</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.014555</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.028779</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.05122</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.200256</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.052428</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.06655999999999999</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.215061</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.598261</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.182769</v>
       </c>
     </row>
     <row r="116">
@@ -8474,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01985</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8504,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005826</v>
       </c>
       <c r="R134" s="3" t="n">
         <v>0</v>
@@ -8532,7 +8532,7 @@
         <v>-0.258084</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.010014</v>
+        <v>-1.029864</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.820945</v>
@@ -14278,7 +14278,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14668,7 +14672,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -17839,7 +17847,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -17924,7 +17936,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -34527,7 +34543,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E266" s="5" t="n">
         <v>-0.09590799999999999</v>
       </c>
@@ -46386,7 +46406,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" s="5" t="n">
         <v>0.09590799999999999</v>
       </c>
